--- a/Oscilo_list.xlsx
+++ b/Oscilo_list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a4087992183cfd69/Documentos/GitHub/oscilografia_TW/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="220" documentId="13_ncr:1_{7027BA24-A038-4EC5-A960-493EB1462A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B08E64A9-1A8F-4DE4-886E-8600C52BD389}"/>
+  <xr:revisionPtr revIDLastSave="241" documentId="13_ncr:1_{7027BA24-A038-4EC5-A960-493EB1462A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A27FCA2-3472-4D4E-9303-E72023595255}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4E59DAF9-8DBB-408C-A814-55F38A18EDAE}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$L$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$L$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="111">
   <si>
     <t>Nome Oscilo</t>
   </si>
@@ -368,6 +368,9 @@
   </si>
   <si>
     <t>TW com equipamento diferente no terminal B</t>
+  </si>
+  <si>
+    <t>2026_03_10_LT_230kV</t>
   </si>
 </sst>
 </file>
@@ -756,7 +759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31C89CCF-5410-44FB-A089-79848F9D5500}">
-  <dimension ref="A1:L82"/>
+  <dimension ref="A1:L83"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.28515625" bestFit="1" customWidth="1"/>
@@ -2505,25 +2508,25 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
@@ -2532,16 +2535,16 @@
         <v>24</v>
       </c>
       <c r="J49" s="2">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="L49" s="2"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>13</v>
@@ -2577,7 +2580,7 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>13</v>
@@ -2613,7 +2616,7 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>13</v>
@@ -2649,7 +2652,7 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>13</v>
@@ -2685,7 +2688,7 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>13</v>
@@ -2721,7 +2724,7 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>13</v>
@@ -2742,7 +2745,7 @@
         <v>14</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>24</v>
@@ -2757,7 +2760,7 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>13</v>
@@ -2793,7 +2796,7 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>13</v>
@@ -2829,7 +2832,7 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>13</v>
@@ -2865,7 +2868,7 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>13</v>
@@ -2901,7 +2904,7 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>13</v>
@@ -2937,7 +2940,7 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>13</v>
@@ -2973,7 +2976,7 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>13</v>
@@ -3009,7 +3012,7 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>13</v>
@@ -3030,7 +3033,7 @@
         <v>14</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>24</v>
@@ -3045,7 +3048,7 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>13</v>
@@ -3066,7 +3069,7 @@
         <v>14</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>24</v>
@@ -3081,7 +3084,7 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>13</v>
@@ -3117,7 +3120,7 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>13</v>
@@ -3153,7 +3156,7 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>13</v>
@@ -3174,7 +3177,7 @@
         <v>14</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>24</v>
@@ -3189,7 +3192,7 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>13</v>
@@ -3225,7 +3228,7 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>13</v>
@@ -3261,7 +3264,7 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>13</v>
@@ -3297,7 +3300,7 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>13</v>
@@ -3333,7 +3336,7 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>13</v>
@@ -3369,7 +3372,7 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>13</v>
@@ -3405,7 +3408,7 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>13</v>
@@ -3426,7 +3429,7 @@
         <v>14</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>24</v>
@@ -3441,7 +3444,7 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>13</v>
@@ -3477,7 +3480,7 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>13</v>
@@ -3513,7 +3516,7 @@
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>13</v>
@@ -3549,7 +3552,7 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>13</v>
@@ -3585,7 +3588,7 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>13</v>
@@ -3621,7 +3624,7 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>13</v>
@@ -3642,7 +3645,7 @@
         <v>14</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>24</v>
@@ -3657,7 +3660,7 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>13</v>
@@ -3678,7 +3681,7 @@
         <v>14</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>24</v>
@@ -3693,10 +3696,10 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>13</v>
@@ -3705,7 +3708,7 @@
         <v>14</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>13</v>
@@ -3714,7 +3717,7 @@
         <v>14</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>24</v>
@@ -3725,12 +3728,48 @@
       <c r="K82" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="L82" s="2" t="s">
+      <c r="L82" s="2"/>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J83" s="2">
+        <v>500</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L83" s="2" t="s">
         <v>63</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L82" xr:uid="{31C89CCF-5410-44FB-A089-79848F9D5500}"/>
+  <autoFilter ref="A1:L83" xr:uid="{31C89CCF-5410-44FB-A089-79848F9D5500}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/Oscilo_list.xlsx
+++ b/Oscilo_list.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a4087992183cfd69/Documentos/GitHub/oscilografia_TW/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="241" documentId="13_ncr:1_{7027BA24-A038-4EC5-A960-493EB1462A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A27FCA2-3472-4D4E-9303-E72023595255}"/>
+  <xr:revisionPtr revIDLastSave="245" documentId="13_ncr:1_{7027BA24-A038-4EC5-A960-493EB1462A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF27C052-6BB2-4A60-A937-F1EABE148487}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4E59DAF9-8DBB-408C-A814-55F38A18EDAE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4E59DAF9-8DBB-408C-A814-55F38A18EDAE}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$L$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$L$84</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="112">
   <si>
     <t>Nome Oscilo</t>
   </si>
@@ -371,6 +371,9 @@
   </si>
   <si>
     <t>2026_03_10_LT_230kV</t>
+  </si>
+  <si>
+    <t>2026_04_05_LT_230kV</t>
   </si>
 </sst>
 </file>
@@ -759,7 +762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31C89CCF-5410-44FB-A089-79848F9D5500}">
-  <dimension ref="A1:L83"/>
+  <dimension ref="A1:L84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.28515625" bestFit="1" customWidth="1"/>
@@ -2544,25 +2547,25 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
@@ -2571,16 +2574,16 @@
         <v>24</v>
       </c>
       <c r="J50" s="2">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="L50" s="2"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>13</v>
@@ -2616,7 +2619,7 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>13</v>
@@ -2652,7 +2655,7 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>13</v>
@@ -2688,7 +2691,7 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>13</v>
@@ -2724,7 +2727,7 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>13</v>
@@ -2760,7 +2763,7 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>13</v>
@@ -2781,7 +2784,7 @@
         <v>14</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>24</v>
@@ -2796,7 +2799,7 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>13</v>
@@ -2832,7 +2835,7 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>13</v>
@@ -2868,7 +2871,7 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>13</v>
@@ -2904,7 +2907,7 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>13</v>
@@ -2940,7 +2943,7 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>13</v>
@@ -2976,7 +2979,7 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>13</v>
@@ -3012,7 +3015,7 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>13</v>
@@ -3048,7 +3051,7 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>13</v>
@@ -3069,7 +3072,7 @@
         <v>14</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>24</v>
@@ -3084,7 +3087,7 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>13</v>
@@ -3105,7 +3108,7 @@
         <v>14</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>24</v>
@@ -3120,7 +3123,7 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>13</v>
@@ -3156,7 +3159,7 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>13</v>
@@ -3192,7 +3195,7 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>13</v>
@@ -3213,7 +3216,7 @@
         <v>14</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>24</v>
@@ -3228,7 +3231,7 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>13</v>
@@ -3264,7 +3267,7 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>13</v>
@@ -3300,7 +3303,7 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>13</v>
@@ -3336,7 +3339,7 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>13</v>
@@ -3372,7 +3375,7 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>13</v>
@@ -3408,7 +3411,7 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>13</v>
@@ -3444,7 +3447,7 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>13</v>
@@ -3465,7 +3468,7 @@
         <v>14</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>24</v>
@@ -3480,7 +3483,7 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>13</v>
@@ -3516,7 +3519,7 @@
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>13</v>
@@ -3552,7 +3555,7 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>13</v>
@@ -3588,7 +3591,7 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>13</v>
@@ -3624,7 +3627,7 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>13</v>
@@ -3660,7 +3663,7 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>13</v>
@@ -3681,7 +3684,7 @@
         <v>14</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>24</v>
@@ -3696,7 +3699,7 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>13</v>
@@ -3717,7 +3720,7 @@
         <v>14</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>24</v>
@@ -3732,10 +3735,10 @@
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>13</v>
@@ -3744,7 +3747,7 @@
         <v>14</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>13</v>
@@ -3753,7 +3756,7 @@
         <v>14</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>24</v>
@@ -3764,12 +3767,48 @@
       <c r="K83" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="L83" s="2" t="s">
+      <c r="L83" s="2"/>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J84" s="2">
+        <v>500</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L84" s="2" t="s">
         <v>63</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L83" xr:uid="{31C89CCF-5410-44FB-A089-79848F9D5500}"/>
+  <autoFilter ref="A1:L84" xr:uid="{31C89CCF-5410-44FB-A089-79848F9D5500}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/Oscilo_list.xlsx
+++ b/Oscilo_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a4087992183cfd69/Documentos/GitHub/oscilografia_TW/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="245" documentId="13_ncr:1_{7027BA24-A038-4EC5-A960-493EB1462A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF27C052-6BB2-4A60-A937-F1EABE148487}"/>
+  <xr:revisionPtr revIDLastSave="259" documentId="13_ncr:1_{7027BA24-A038-4EC5-A960-493EB1462A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E0B6DE4-B798-426D-9966-B14F81CCCC05}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4E59DAF9-8DBB-408C-A814-55F38A18EDAE}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$L$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$L$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="114">
   <si>
     <t>Nome Oscilo</t>
   </si>
@@ -374,6 +374,12 @@
   </si>
   <si>
     <t>2026_04_05_LT_230kV</t>
+  </si>
+  <si>
+    <t>2026_07_11_LT_230 kV</t>
+  </si>
+  <si>
+    <t>Falta interna a uma LT com localização de falta, mas em equipamento em outra LT</t>
   </si>
 </sst>
 </file>
@@ -463,6 +469,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -762,7 +772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31C89CCF-5410-44FB-A089-79848F9D5500}">
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:L85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.28515625" bestFit="1" customWidth="1"/>
@@ -776,7 +786,7 @@
     <col min="9" max="9" width="11.28515625" customWidth="1"/>
     <col min="10" max="10" width="11.140625" customWidth="1"/>
     <col min="11" max="11" width="17.42578125" customWidth="1"/>
-    <col min="12" max="12" width="49.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="79.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -2583,7 +2593,7 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>13</v>
@@ -2592,34 +2602,36 @@
         <v>13</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J51" s="2">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="L51" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>13</v>
@@ -2655,7 +2667,7 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>13</v>
@@ -2691,7 +2703,7 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>13</v>
@@ -2727,7 +2739,7 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>13</v>
@@ -2763,7 +2775,7 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>13</v>
@@ -2799,7 +2811,7 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>13</v>
@@ -2820,7 +2832,7 @@
         <v>14</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>24</v>
@@ -2835,7 +2847,7 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>13</v>
@@ -2871,7 +2883,7 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>13</v>
@@ -2907,7 +2919,7 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>13</v>
@@ -2943,7 +2955,7 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>13</v>
@@ -2979,7 +2991,7 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>13</v>
@@ -3015,7 +3027,7 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>13</v>
@@ -3051,7 +3063,7 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>13</v>
@@ -3087,7 +3099,7 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>13</v>
@@ -3108,7 +3120,7 @@
         <v>14</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>24</v>
@@ -3123,7 +3135,7 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>13</v>
@@ -3144,7 +3156,7 @@
         <v>14</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>24</v>
@@ -3159,7 +3171,7 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>13</v>
@@ -3195,7 +3207,7 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>13</v>
@@ -3231,7 +3243,7 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>13</v>
@@ -3252,7 +3264,7 @@
         <v>14</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>24</v>
@@ -3267,7 +3279,7 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>13</v>
@@ -3303,7 +3315,7 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>13</v>
@@ -3339,7 +3351,7 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>13</v>
@@ -3375,7 +3387,7 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>13</v>
@@ -3411,7 +3423,7 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>13</v>
@@ -3447,7 +3459,7 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>13</v>
@@ -3483,7 +3495,7 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>13</v>
@@ -3504,7 +3516,7 @@
         <v>14</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>24</v>
@@ -3519,7 +3531,7 @@
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>13</v>
@@ -3555,7 +3567,7 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>13</v>
@@ -3591,7 +3603,7 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>13</v>
@@ -3627,7 +3639,7 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>13</v>
@@ -3663,7 +3675,7 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>13</v>
@@ -3699,7 +3711,7 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>13</v>
@@ -3720,7 +3732,7 @@
         <v>14</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>24</v>
@@ -3735,7 +3747,7 @@
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>13</v>
@@ -3756,7 +3768,7 @@
         <v>14</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>24</v>
@@ -3771,10 +3783,10 @@
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>13</v>
@@ -3783,7 +3795,7 @@
         <v>14</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>13</v>
@@ -3792,7 +3804,7 @@
         <v>14</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="I84" s="2" t="s">
         <v>24</v>
@@ -3803,12 +3815,48 @@
       <c r="K84" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="L84" s="2" t="s">
+      <c r="L84" s="2"/>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J85" s="2">
+        <v>500</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L85" s="2" t="s">
         <v>63</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L84" xr:uid="{31C89CCF-5410-44FB-A089-79848F9D5500}"/>
+  <autoFilter ref="A1:L85" xr:uid="{31C89CCF-5410-44FB-A089-79848F9D5500}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>